--- a/Result/profitability/4142.xlsx
+++ b/Result/profitability/4142.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.105</v>
+        <v>-0.23</v>
       </c>
       <c r="N2" t="n">
-        <v>-18.02125000000003</v>
+        <v>-35.98250000000003</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.36</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2275</v>
+        <v>-0.26125</v>
       </c>
       <c r="N3" t="n">
-        <v>-21.98000000000003</v>
+        <v>-36.33875000000003</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.25125</v>
+        <v>-0.2325</v>
       </c>
       <c r="N4" t="n">
-        <v>-21.16875000000003</v>
+        <v>-11.90750000000003</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>4.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0.31875</v>
+        <v>0.33625</v>
       </c>
       <c r="N5" t="n">
-        <v>9.502499999999971</v>
+        <v>2.812499999999971</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>2.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6375</v>
+        <v>0.595</v>
       </c>
       <c r="N6" t="n">
-        <v>24.63374999999997</v>
+        <v>10.64874999999997</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5874999999999999</v>
+        <v>0.4750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>4.553749999999969</v>
+        <v>-13.40625000000003</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4525</v>
+        <v>0.46</v>
       </c>
       <c r="N8" t="n">
-        <v>2.18624999999997</v>
+        <v>1.743749999999971</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -8709,15 +8709,15 @@
         <v>-40.6</v>
       </c>
       <c r="G66" t="n">
-        <v>-207</v>
+        <v>-205</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-190.36%</t>
+          <t>-188.83%</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="J66" t="n">
         <v>-237</v>
@@ -8836,15 +8836,15 @@
         <v>17.76</v>
       </c>
       <c r="G67" t="n">
-        <v>-60</v>
+        <v>-62</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-12.67%</t>
+          <t>-13.01%</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
         <v>-39</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4142</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>67</v>
+      </c>
+      <c r="D70" t="n">
+        <v>130</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-94.12</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-173</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-258.72%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-173</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-160</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-31.98375000000003</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-0.1363636363636364</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>-3.540000000000006</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.03908147493928027</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-0.2692307692307693</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-53.52</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.318226600985222</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
